--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -737,7 +737,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -737,7 +737,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -737,7 +737,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -737,7 +737,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -521,223 +528,230 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>14 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_id</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>disenos</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: disenos</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>grupo_de_comparacion_firmado_2026_09_22</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: grupo_de_comparacion_firmado_2026_09_22</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>grupo_sin_fago</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: grupo_sin_fago</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>contraste_para_p_aeruginosa</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: contraste_para_p_aeruginosa</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>brazo_control_identificado</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: brazo_control_identificado</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>tipo_y_unidad_de_asignacion</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: tipo_y_unidad_de_asignacion</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>tiempo_cero</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: tiempo_cero</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>tiempo_de_evaluacion_del_desenlace</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: tiempo_de_evaluacion_del_desenlace</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>cointervenciones_y_antibiotico_concomitante</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: cointervenciones_y_antibiotico_concomitante</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>perdidas_y_datos_faltantes</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: perdidas_y_datos_faltantes</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>estimando_reportado</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: estimando_reportado</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>hay_contraste_extraible</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>columna interna: hay_contraste_extraible</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>firmado_por</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>columna interna: firmado_por</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>columna interna: fecha</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -773,77 +787,77 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>disenos</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>grupo_de_comparacion_firmado_2026_09_22</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>grupo_sin_fago</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>contraste_para_p_aeruginosa</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>brazo_control_identificado</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>tipo_y_unidad_de_asignacion</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>tiempo_cero</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>tiempo_de_evaluacion_del_desenlace</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>cointervenciones_y_antibiotico_concomitante</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>perdidas_y_datos_faltantes</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>estimando_reportado</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>hay_contraste_extraible</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>firmado_por</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -751,7 +751,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -751,7 +751,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sección 3.7. «Grupo sin fago» y «contraste para P. aeruginosa» son la codificación del texto firmado que va al lado.</t>
+          <t>Sección 3.7. «Grupo sin fago» y «Contraste para P. aeruginosa» los derivó el modelo de lenguaje (ingest_lectura_firmada.py) del texto que los dos autores firmaron en la relectura del 30 de septiembre de 2026 y que va al lado: lo firmado es ese texto, no su codificación.</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>disenos</t>
+          <t>Diseños</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>grupo_de_comparacion_firmado_2026_09_22</t>
+          <t>Grupo de comparación (firmado el 2026-09-22)</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>grupo_sin_fago</t>
+          <t>Grupo sin fago (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>contraste_para_p_aeruginosa</t>
+          <t>Contraste para P. aeruginosa (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>brazo_control_identificado</t>
+          <t>Brazo control identificado</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>tipo_y_unidad_de_asignacion</t>
+          <t>Tipo y unidad de asignación</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>tiempo_cero</t>
+          <t>Tiempo cero</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>tiempo_de_evaluacion_del_desenlace</t>
+          <t>Tiempo de evaluación del desenlace</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>cointervenciones_y_antibiotico_concomitante</t>
+          <t>Cointervenciones y antibiótico concomitante</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>perdidas_y_datos_faltantes</t>
+          <t>Pérdidas y datos faltantes</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>estimando_reportado</t>
+          <t>Estimando reportado</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>hay_contraste_extraible</t>
+          <t>¿Hay contraste extraíble?</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>firmado_por</t>
+          <t>Firmado por</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -794,67 +794,67 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>disenos</t>
+          <t>Diseños</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>grupo_de_comparacion_firmado_2026_09_22</t>
+          <t>Grupo de comparación (firmado el 2026-09-22)</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>grupo_sin_fago</t>
+          <t>Grupo sin fago (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>contraste_para_p_aeruginosa</t>
+          <t>Contraste para P. aeruginosa (lo codificó el modelo)</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>brazo_control_identificado</t>
+          <t>Brazo control identificado</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>tipo_y_unidad_de_asignacion</t>
+          <t>Tipo y unidad de asignación</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>tiempo_cero</t>
+          <t>Tiempo cero</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>tiempo_de_evaluacion_del_desenlace</t>
+          <t>Tiempo de evaluación del desenlace</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>cointervenciones_y_antibiotico_concomitante</t>
+          <t>Cointervenciones y antibiótico concomitante</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>perdidas_y_datos_faltantes</t>
+          <t>Pérdidas y datos faltantes</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>estimando_reportado</t>
+          <t>Estimando reportado</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>hay_contraste_extraible</t>
+          <t>¿Hay contraste extraíble?</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>firmado_por</t>
+          <t>Firmado por</t>
         </is>
       </c>
       <c r="O1" s="9" t="inlineStr">

--- a/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
+++ b/verificables revisión sistemática/S24_comparativos_reextraidos.xlsx
@@ -751,7 +751,7 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
